--- a/売上管理_受注ログ版 (6).xlsx
+++ b/売上管理_受注ログ版 (6).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jet35\Desktop\小原\__予算確認用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\重要AI用\売上ルーム\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C573F3FC-34AA-4A44-9E01-209F973F510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786EF222-800B-451F-A9C9-D35E1818E354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="1620" windowWidth="25245" windowHeight="13755" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="サマリー" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -2251,14 +2242,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2789,15 +2780,15 @@
       </c>
       <c r="C26" s="14">
         <f ca="1">INDEX(週次集計!D3:D56,$B$20)</f>
-        <v>0</v>
+        <v>387801</v>
       </c>
       <c r="D26" s="15">
         <f ca="1">IFERROR(C26/B26,0)</f>
-        <v>0</v>
+        <v>1.551204</v>
       </c>
       <c r="E26" s="14">
         <f ca="1">MAX(B26-C26,0)</f>
-        <v>250000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2810,15 +2801,15 @@
       </c>
       <c r="C27" s="14">
         <f ca="1">INDEX(週次集計!E3:E56,$B$20)</f>
-        <v>0</v>
+        <v>22829</v>
       </c>
       <c r="D27" s="15">
         <f ca="1">IFERROR(C27/B27,0)</f>
-        <v>0</v>
+        <v>9.1315999999999994E-2</v>
       </c>
       <c r="E27" s="14">
         <f ca="1">MAX(B27-C27,0)</f>
-        <v>250000</v>
+        <v>227171</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2831,15 +2822,15 @@
       </c>
       <c r="C28" s="14">
         <f ca="1">INDEX(月次集計!D3:D15,$B$21)</f>
-        <v>841291</v>
+        <v>1229092</v>
       </c>
       <c r="D28" s="15">
         <f ca="1">IFERROR(C28/B28,0)</f>
-        <v>0.84129100000000001</v>
+        <v>1.2290920000000001</v>
       </c>
       <c r="E28" s="14">
         <f ca="1">MAX(B28-C28,0)</f>
-        <v>158709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2852,15 +2843,15 @@
       </c>
       <c r="C29" s="14">
         <f ca="1">INDEX(月次集計!E3:E15,$B$21)</f>
-        <v>519119</v>
+        <v>541948</v>
       </c>
       <c r="D29" s="15">
         <f ca="1">IFERROR(C29/B29,0)</f>
-        <v>0.519119</v>
+        <v>0.54194799999999999</v>
       </c>
       <c r="E29" s="14">
         <f ca="1">MAX(B29-C29,0)</f>
-        <v>480881</v>
+        <v>458052</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2904,11 +2895,11 @@
       </c>
       <c r="C34" s="14">
         <f ca="1">INDEX(週次集計!D3:D56,$B$20)</f>
-        <v>0</v>
+        <v>387801</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" ref="D34:D41" ca="1" si="0">MAX(B34-C34,0)</f>
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="E34" s="17">
         <f ca="1">INDEX(週次集計!C3:C56,$B$20)</f>
@@ -2920,11 +2911,11 @@
       </c>
       <c r="G34" s="14">
         <f t="shared" ref="G34:G41" ca="1" si="2">IFERROR(D34/F34,0)</f>
-        <v>62500</v>
+        <v>0</v>
       </c>
       <c r="H34" s="19">
         <f t="shared" ref="H34:H41" ca="1" si="3">RANK(G34,$G$34:$G$41)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2937,11 +2928,11 @@
       </c>
       <c r="C35" s="14">
         <f ca="1">INDEX(週次集計!E3:E56,$B$20)</f>
-        <v>0</v>
+        <v>22829</v>
       </c>
       <c r="D35" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>250000</v>
+        <v>227171</v>
       </c>
       <c r="E35" s="17">
         <f ca="1">INDEX(週次集計!C3:C56,$B$20)</f>
@@ -2953,11 +2944,11 @@
       </c>
       <c r="G35" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>62500</v>
+        <v>56792.75</v>
       </c>
       <c r="H35" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2970,11 +2961,11 @@
       </c>
       <c r="C36" s="14">
         <f ca="1">INDEX(週次集計!F3:F56,$B$20)</f>
-        <v>0</v>
+        <v>410630</v>
       </c>
       <c r="D36" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>500000</v>
+        <v>89370</v>
       </c>
       <c r="E36" s="17">
         <f ca="1">INDEX(週次集計!C3:C56,$B$20)</f>
@@ -2986,11 +2977,11 @@
       </c>
       <c r="G36" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>125000</v>
+        <v>22342.5</v>
       </c>
       <c r="H36" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -3003,11 +2994,11 @@
       </c>
       <c r="C37" s="14">
         <f ca="1">INDEX(月次集計!D3:D15,$B$21)</f>
-        <v>841291</v>
+        <v>1229092</v>
       </c>
       <c r="D37" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>158709</v>
+        <v>0</v>
       </c>
       <c r="E37" s="17">
         <f ca="1">INDEX(月次集計!C3:C15,$B$21)</f>
@@ -3019,11 +3010,11 @@
       </c>
       <c r="G37" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>22672.714285714286</v>
+        <v>0</v>
       </c>
       <c r="H37" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3036,11 +3027,11 @@
       </c>
       <c r="C38" s="14">
         <f ca="1">INDEX(月次集計!E3:E15,$B$21)</f>
-        <v>519119</v>
+        <v>541948</v>
       </c>
       <c r="D38" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>480881</v>
+        <v>458052</v>
       </c>
       <c r="E38" s="17">
         <f ca="1">INDEX(月次集計!C3:C15,$B$21)</f>
@@ -3052,11 +3043,11 @@
       </c>
       <c r="G38" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>68697.28571428571</v>
+        <v>65436</v>
       </c>
       <c r="H38" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3069,11 +3060,11 @@
       </c>
       <c r="C39" s="14">
         <f ca="1">INDEX(月次集計!F3:F15,$B$21)</f>
-        <v>1360410</v>
+        <v>1771040</v>
       </c>
       <c r="D39" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>639590</v>
+        <v>228960</v>
       </c>
       <c r="E39" s="17">
         <f ca="1">INDEX(月次集計!C3:C15,$B$21)</f>
@@ -3085,11 +3076,11 @@
       </c>
       <c r="G39" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>91370</v>
+        <v>32708.571428571428</v>
       </c>
       <c r="H39" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3102,11 +3093,11 @@
       </c>
       <c r="C40" s="14">
         <f ca="1">INDEX(半期年間集計!F3:F5,IF($B$22="上半期",1,2))</f>
-        <v>5235243</v>
+        <v>5645873</v>
       </c>
       <c r="D40" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>6764757</v>
+        <v>6354127</v>
       </c>
       <c r="E40" s="17">
         <f ca="1">INDEX(半期年間集計!C3:C5,IF($B$22="上半期",1,2))</f>
@@ -3118,7 +3109,7 @@
       </c>
       <c r="G40" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>178019.92105263157</v>
+        <v>167213.86842105264</v>
       </c>
       <c r="H40" s="19">
         <f t="shared" ca="1" si="3"/>
@@ -3135,11 +3126,11 @@
       </c>
       <c r="C41" s="14">
         <f>INDEX(半期年間集計!F3:F5,3)</f>
-        <v>5235243</v>
+        <v>5645873</v>
       </c>
       <c r="D41" s="14">
         <f t="shared" si="0"/>
-        <v>18764757</v>
+        <v>18354127</v>
       </c>
       <c r="E41" s="17">
         <f>INDEX(半期年間集計!C3:C5,3)</f>
@@ -3151,48 +3142,48 @@
       </c>
       <c r="G41" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>85683.821917808222</v>
+        <v>83808.799086757994</v>
       </c>
       <c r="H41" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="41" t="s">
+      <c r="A43" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="41"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="41" t="s">
+      <c r="A44" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="41"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
@@ -3403,16 +3394,16 @@
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="40" t="s">
+      <c r="A61" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B61" s="40"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="40"/>
-      <c r="E61" s="40"/>
-      <c r="F61" s="40"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="40"/>
+      <c r="B61" s="39"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3487,34 +3478,34 @@
       <c r="X1" s="37"/>
       <c r="Y1" s="37"/>
       <c r="Z1" s="37"/>
-      <c r="AB1" s="40" t="s">
+      <c r="AB1" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-      <c r="AO1" s="40"/>
-      <c r="AP1" s="40"/>
-      <c r="AQ1" s="40"/>
-      <c r="AR1" s="40"/>
-      <c r="AS1" s="40"/>
-      <c r="AT1" s="40"/>
-      <c r="AU1" s="40"/>
-      <c r="AV1" s="40"/>
-      <c r="AW1" s="40"/>
-      <c r="AX1" s="40"/>
-      <c r="AY1" s="40"/>
-      <c r="AZ1" s="40"/>
-      <c r="BA1" s="40"/>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="39"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
+      <c r="AH1" s="39"/>
+      <c r="AI1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="39"/>
+      <c r="AV1" s="39"/>
+      <c r="AW1" s="39"/>
+      <c r="AX1" s="39"/>
+      <c r="AY1" s="39"/>
+      <c r="AZ1" s="39"/>
+      <c r="BA1" s="39"/>
     </row>
     <row r="2" spans="1:53" ht="24" customHeight="1">
       <c r="A2" s="21"/>
@@ -3539,52 +3530,52 @@
       <c r="H2" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="40" t="s">
+      <c r="AB2" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="40"/>
-      <c r="AK2" s="40"/>
-      <c r="AL2" s="40"/>
-      <c r="AM2" s="40"/>
-      <c r="AN2" s="40"/>
-      <c r="AO2" s="40"/>
-      <c r="AP2" s="40"/>
-      <c r="AQ2" s="40"/>
-      <c r="AR2" s="40"/>
-      <c r="AS2" s="40"/>
-      <c r="AT2" s="40"/>
-      <c r="AU2" s="40"/>
-      <c r="AV2" s="40"/>
-      <c r="AW2" s="40"/>
-      <c r="AX2" s="40"/>
-      <c r="AY2" s="40"/>
-      <c r="AZ2" s="40"/>
-      <c r="BA2" s="40"/>
+      <c r="AC2" s="39"/>
+      <c r="AD2" s="39"/>
+      <c r="AE2" s="39"/>
+      <c r="AF2" s="39"/>
+      <c r="AG2" s="39"/>
+      <c r="AH2" s="39"/>
+      <c r="AI2" s="39"/>
+      <c r="AJ2" s="39"/>
+      <c r="AK2" s="39"/>
+      <c r="AL2" s="39"/>
+      <c r="AM2" s="39"/>
+      <c r="AN2" s="39"/>
+      <c r="AO2" s="39"/>
+      <c r="AP2" s="39"/>
+      <c r="AQ2" s="39"/>
+      <c r="AR2" s="39"/>
+      <c r="AS2" s="39"/>
+      <c r="AT2" s="39"/>
+      <c r="AU2" s="39"/>
+      <c r="AV2" s="39"/>
+      <c r="AW2" s="39"/>
+      <c r="AX2" s="39"/>
+      <c r="AY2" s="39"/>
+      <c r="AZ2" s="39"/>
+      <c r="BA2" s="39"/>
     </row>
     <row r="3" spans="1:53" ht="19.5" customHeight="1">
       <c r="A3" s="23"/>
       <c r="B3" s="23">
         <f ca="1">MAX(サマリー!$B$7-INDEX(週次集計!$D$3:$D$56,サマリー!$B$20),0)</f>
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="C3" s="23">
         <f ca="1">MAX(サマリー!$B$7-INDEX(週次集計!$E$3:$E$56,サマリー!$B$20),0)</f>
-        <v>250000</v>
+        <v>227171</v>
       </c>
       <c r="D3" s="23">
         <f ca="1">INDEX(週次集計!$F$3:$F$56,サマリー!$B$20)</f>
-        <v>0</v>
+        <v>410630</v>
       </c>
       <c r="E3" s="23">
         <f ca="1">MAX(サマリー!$B$15-INDEX(週次集計!$F$3:$F$56,サマリー!$B$20),0)</f>
-        <v>500000</v>
+        <v>89370</v>
       </c>
       <c r="F3" s="23">
         <f ca="1">SUMIFS($C$6:$C$205,$B$6:$B$205,TODAY())</f>
@@ -3598,86 +3589,86 @@
         <f ca="1">F3+G3</f>
         <v>0</v>
       </c>
-      <c r="AB3" s="41" t="s">
+      <c r="AB3" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
-      <c r="AR3" s="41"/>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="41"/>
-      <c r="AU3" s="41"/>
-      <c r="AV3" s="41"/>
-      <c r="AW3" s="41"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="41"/>
-      <c r="AZ3" s="41"/>
-      <c r="BA3" s="41"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="38"/>
+      <c r="AK3" s="38"/>
+      <c r="AL3" s="38"/>
+      <c r="AM3" s="38"/>
+      <c r="AN3" s="38"/>
+      <c r="AO3" s="38"/>
+      <c r="AP3" s="38"/>
+      <c r="AQ3" s="38"/>
+      <c r="AR3" s="38"/>
+      <c r="AS3" s="38"/>
+      <c r="AT3" s="38"/>
+      <c r="AU3" s="38"/>
+      <c r="AV3" s="38"/>
+      <c r="AW3" s="38"/>
+      <c r="AX3" s="38"/>
+      <c r="AY3" s="38"/>
+      <c r="AZ3" s="38"/>
+      <c r="BA3" s="38"/>
     </row>
     <row r="4" spans="1:53" ht="19.5" customHeight="1">
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="39" t="s">
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="T4" s="39"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="39"/>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="39"/>
-      <c r="AB4" s="41" t="s">
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AB4" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="AC4" s="41"/>
-      <c r="AD4" s="41"/>
-      <c r="AE4" s="41"/>
-      <c r="AF4" s="41"/>
-      <c r="AG4" s="41"/>
-      <c r="AH4" s="41"/>
-      <c r="AI4" s="41"/>
-      <c r="AJ4" s="41"/>
-      <c r="AK4" s="41"/>
-      <c r="AL4" s="41"/>
-      <c r="AM4" s="41"/>
-      <c r="AN4" s="41"/>
-      <c r="AO4" s="41"/>
-      <c r="AP4" s="41"/>
-      <c r="AQ4" s="41"/>
-      <c r="AR4" s="41"/>
-      <c r="AS4" s="41"/>
-      <c r="AT4" s="41"/>
-      <c r="AU4" s="41"/>
-      <c r="AV4" s="41"/>
-      <c r="AW4" s="41"/>
-      <c r="AX4" s="41"/>
-      <c r="AY4" s="41"/>
-      <c r="AZ4" s="41"/>
-      <c r="BA4" s="41"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="38"/>
+      <c r="AK4" s="38"/>
+      <c r="AL4" s="38"/>
+      <c r="AM4" s="38"/>
+      <c r="AN4" s="38"/>
+      <c r="AO4" s="38"/>
+      <c r="AP4" s="38"/>
+      <c r="AQ4" s="38"/>
+      <c r="AR4" s="38"/>
+      <c r="AS4" s="38"/>
+      <c r="AT4" s="38"/>
+      <c r="AU4" s="38"/>
+      <c r="AV4" s="38"/>
+      <c r="AW4" s="38"/>
+      <c r="AX4" s="38"/>
+      <c r="AY4" s="38"/>
+      <c r="AZ4" s="38"/>
+      <c r="BA4" s="38"/>
     </row>
     <row r="5" spans="1:53" ht="31.5" customHeight="1">
       <c r="A5" s="12" t="s">
@@ -3752,34 +3743,34 @@
       <c r="Z5" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="AB5" s="41" t="s">
+      <c r="AB5" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="AC5" s="41"/>
-      <c r="AD5" s="41"/>
-      <c r="AE5" s="41"/>
-      <c r="AF5" s="41"/>
-      <c r="AG5" s="41"/>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="41"/>
-      <c r="AJ5" s="41"/>
-      <c r="AK5" s="41"/>
-      <c r="AL5" s="41"/>
-      <c r="AM5" s="41"/>
-      <c r="AN5" s="41"/>
-      <c r="AO5" s="41"/>
-      <c r="AP5" s="41"/>
-      <c r="AQ5" s="41"/>
-      <c r="AR5" s="41"/>
-      <c r="AS5" s="41"/>
-      <c r="AT5" s="41"/>
-      <c r="AU5" s="41"/>
-      <c r="AV5" s="41"/>
-      <c r="AW5" s="41"/>
-      <c r="AX5" s="41"/>
-      <c r="AY5" s="41"/>
-      <c r="AZ5" s="41"/>
-      <c r="BA5" s="41"/>
+      <c r="AC5" s="38"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="38"/>
+      <c r="AG5" s="38"/>
+      <c r="AH5" s="38"/>
+      <c r="AI5" s="38"/>
+      <c r="AJ5" s="38"/>
+      <c r="AK5" s="38"/>
+      <c r="AL5" s="38"/>
+      <c r="AM5" s="38"/>
+      <c r="AN5" s="38"/>
+      <c r="AO5" s="38"/>
+      <c r="AP5" s="38"/>
+      <c r="AQ5" s="38"/>
+      <c r="AR5" s="38"/>
+      <c r="AS5" s="38"/>
+      <c r="AT5" s="38"/>
+      <c r="AU5" s="38"/>
+      <c r="AV5" s="38"/>
+      <c r="AW5" s="38"/>
+      <c r="AX5" s="38"/>
+      <c r="AY5" s="38"/>
+      <c r="AZ5" s="38"/>
+      <c r="BA5" s="38"/>
     </row>
     <row r="6" spans="1:53">
       <c r="A6" s="24"/>
@@ -3820,34 +3811,34 @@
       <c r="X6" s="24"/>
       <c r="Y6" s="24"/>
       <c r="Z6" s="24"/>
-      <c r="AB6" s="40" t="s">
+      <c r="AB6" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="40"/>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="40"/>
-      <c r="AK6" s="40"/>
-      <c r="AL6" s="40"/>
-      <c r="AM6" s="40"/>
-      <c r="AN6" s="40"/>
-      <c r="AO6" s="40"/>
-      <c r="AP6" s="40"/>
-      <c r="AQ6" s="40"/>
-      <c r="AR6" s="40"/>
-      <c r="AS6" s="40"/>
-      <c r="AT6" s="40"/>
-      <c r="AU6" s="40"/>
-      <c r="AV6" s="40"/>
-      <c r="AW6" s="40"/>
-      <c r="AX6" s="40"/>
-      <c r="AY6" s="40"/>
-      <c r="AZ6" s="40"/>
-      <c r="BA6" s="40"/>
+      <c r="AC6" s="39"/>
+      <c r="AD6" s="39"/>
+      <c r="AE6" s="39"/>
+      <c r="AF6" s="39"/>
+      <c r="AG6" s="39"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="39"/>
+      <c r="AL6" s="39"/>
+      <c r="AM6" s="39"/>
+      <c r="AN6" s="39"/>
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="39"/>
+      <c r="AQ6" s="39"/>
+      <c r="AR6" s="39"/>
+      <c r="AS6" s="39"/>
+      <c r="AT6" s="39"/>
+      <c r="AU6" s="39"/>
+      <c r="AV6" s="39"/>
+      <c r="AW6" s="39"/>
+      <c r="AX6" s="39"/>
+      <c r="AY6" s="39"/>
+      <c r="AZ6" s="39"/>
+      <c r="BA6" s="39"/>
     </row>
     <row r="7" spans="1:53">
       <c r="A7" s="28">
@@ -18538,11 +18529,11 @@
         <v>46145</v>
       </c>
       <c r="D3" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B3,受注ログ!$B$4:$B$205,"&lt;="&amp;C3)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B3,受注ログ!$B$4:$B$5000,"&lt;="&amp;C3)</f>
         <v>0</v>
       </c>
       <c r="E3" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B3,受注ログ!$B$4:$B$205,"&lt;="&amp;C3)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B3,受注ログ!$B$4:$B$5000,"&lt;="&amp;C3)</f>
         <v>0</v>
       </c>
       <c r="F3" s="14">
@@ -18583,11 +18574,11 @@
         <v>46152</v>
       </c>
       <c r="D4" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B4,受注ログ!$B$4:$B$205,"&lt;="&amp;C4)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B4,受注ログ!$B$4:$B$5000,"&lt;="&amp;C4)</f>
         <v>0</v>
       </c>
       <c r="E4" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B4,受注ログ!$B$4:$B$205,"&lt;="&amp;C4)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B4,受注ログ!$B$4:$B$5000,"&lt;="&amp;C4)</f>
         <v>0</v>
       </c>
       <c r="F4" s="14">
@@ -18628,11 +18619,11 @@
         <v>46159</v>
       </c>
       <c r="D5" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B5,受注ログ!$B$4:$B$205,"&lt;="&amp;C5)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B5,受注ログ!$B$4:$B$5000,"&lt;="&amp;C5)</f>
         <v>0</v>
       </c>
       <c r="E5" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B5,受注ログ!$B$4:$B$205,"&lt;="&amp;C5)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B5,受注ログ!$B$4:$B$5000,"&lt;="&amp;C5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="14">
@@ -18673,11 +18664,11 @@
         <v>46166</v>
       </c>
       <c r="D6" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B6,受注ログ!$B$4:$B$205,"&lt;="&amp;C6)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B6,受注ログ!$B$4:$B$5000,"&lt;="&amp;C6)</f>
         <v>0</v>
       </c>
       <c r="E6" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B6,受注ログ!$B$4:$B$205,"&lt;="&amp;C6)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B6,受注ログ!$B$4:$B$5000,"&lt;="&amp;C6)</f>
         <v>0</v>
       </c>
       <c r="F6" s="14">
@@ -18718,11 +18709,11 @@
         <v>46173</v>
       </c>
       <c r="D7" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B7,受注ログ!$B$4:$B$205,"&lt;="&amp;C7)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B7,受注ログ!$B$4:$B$5000,"&lt;="&amp;C7)</f>
         <v>0</v>
       </c>
       <c r="E7" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B7,受注ログ!$B$4:$B$205,"&lt;="&amp;C7)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B7,受注ログ!$B$4:$B$5000,"&lt;="&amp;C7)</f>
         <v>0</v>
       </c>
       <c r="F7" s="14">
@@ -18763,11 +18754,11 @@
         <v>46180</v>
       </c>
       <c r="D8" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B8,受注ログ!$B$4:$B$205,"&lt;="&amp;C8)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B8,受注ログ!$B$4:$B$5000,"&lt;="&amp;C8)</f>
         <v>0</v>
       </c>
       <c r="E8" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B8,受注ログ!$B$4:$B$205,"&lt;="&amp;C8)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B8,受注ログ!$B$4:$B$5000,"&lt;="&amp;C8)</f>
         <v>0</v>
       </c>
       <c r="F8" s="14">
@@ -18808,11 +18799,11 @@
         <v>46187</v>
       </c>
       <c r="D9" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B9,受注ログ!$B$4:$B$205,"&lt;="&amp;C9)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B9,受注ログ!$B$4:$B$5000,"&lt;="&amp;C9)</f>
         <v>0</v>
       </c>
       <c r="E9" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B9,受注ログ!$B$4:$B$205,"&lt;="&amp;C9)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B9,受注ログ!$B$4:$B$5000,"&lt;="&amp;C9)</f>
         <v>0</v>
       </c>
       <c r="F9" s="14">
@@ -18853,11 +18844,11 @@
         <v>46194</v>
       </c>
       <c r="D10" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B10,受注ログ!$B$4:$B$205,"&lt;="&amp;C10)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B10,受注ログ!$B$4:$B$5000,"&lt;="&amp;C10)</f>
         <v>0</v>
       </c>
       <c r="E10" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B10,受注ログ!$B$4:$B$205,"&lt;="&amp;C10)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B10,受注ログ!$B$4:$B$5000,"&lt;="&amp;C10)</f>
         <v>0</v>
       </c>
       <c r="F10" s="14">
@@ -18898,11 +18889,11 @@
         <v>46201</v>
       </c>
       <c r="D11" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B11,受注ログ!$B$4:$B$205,"&lt;="&amp;C11)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B11,受注ログ!$B$4:$B$5000,"&lt;="&amp;C11)</f>
         <v>0</v>
       </c>
       <c r="E11" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B11,受注ログ!$B$4:$B$205,"&lt;="&amp;C11)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B11,受注ログ!$B$4:$B$5000,"&lt;="&amp;C11)</f>
         <v>0</v>
       </c>
       <c r="F11" s="14">
@@ -18943,11 +18934,11 @@
         <v>46208</v>
       </c>
       <c r="D12" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B12,受注ログ!$B$4:$B$205,"&lt;="&amp;C12)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B12,受注ログ!$B$4:$B$5000,"&lt;="&amp;C12)</f>
         <v>245666</v>
       </c>
       <c r="E12" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B12,受注ログ!$B$4:$B$205,"&lt;="&amp;C12)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B12,受注ログ!$B$4:$B$5000,"&lt;="&amp;C12)</f>
         <v>90837</v>
       </c>
       <c r="F12" s="14">
@@ -18988,11 +18979,11 @@
         <v>46215</v>
       </c>
       <c r="D13" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B13,受注ログ!$B$4:$B$205,"&lt;="&amp;C13)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B13,受注ログ!$B$4:$B$5000,"&lt;="&amp;C13)</f>
         <v>134517</v>
       </c>
       <c r="E13" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B13,受注ログ!$B$4:$B$205,"&lt;="&amp;C13)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B13,受注ログ!$B$4:$B$5000,"&lt;="&amp;C13)</f>
         <v>172580</v>
       </c>
       <c r="F13" s="14">
@@ -19033,11 +19024,11 @@
         <v>46222</v>
       </c>
       <c r="D14" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B14,受注ログ!$B$4:$B$205,"&lt;="&amp;C14)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B14,受注ログ!$B$4:$B$5000,"&lt;="&amp;C14)</f>
         <v>261339</v>
       </c>
       <c r="E14" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B14,受注ログ!$B$4:$B$205,"&lt;="&amp;C14)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B14,受注ログ!$B$4:$B$5000,"&lt;="&amp;C14)</f>
         <v>88808</v>
       </c>
       <c r="F14" s="14">
@@ -19078,11 +19069,11 @@
         <v>46229</v>
       </c>
       <c r="D15" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B15,受注ログ!$B$4:$B$205,"&lt;="&amp;C15)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B15,受注ログ!$B$4:$B$5000,"&lt;="&amp;C15)</f>
         <v>292030</v>
       </c>
       <c r="E15" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B15,受注ログ!$B$4:$B$205,"&lt;="&amp;C15)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B15,受注ログ!$B$4:$B$5000,"&lt;="&amp;C15)</f>
         <v>206335</v>
       </c>
       <c r="F15" s="14">
@@ -19123,11 +19114,11 @@
         <v>46236</v>
       </c>
       <c r="D16" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B16,受注ログ!$B$4:$B$205,"&lt;="&amp;C16)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B16,受注ログ!$B$4:$B$5000,"&lt;="&amp;C16)</f>
         <v>382208</v>
       </c>
       <c r="E16" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B16,受注ログ!$B$4:$B$205,"&lt;="&amp;C16)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B16,受注ログ!$B$4:$B$5000,"&lt;="&amp;C16)</f>
         <v>176366</v>
       </c>
       <c r="F16" s="14">
@@ -19168,11 +19159,11 @@
         <v>46243</v>
       </c>
       <c r="D17" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B17,受注ログ!$B$4:$B$205,"&lt;="&amp;C17)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B17,受注ログ!$B$4:$B$5000,"&lt;="&amp;C17)</f>
         <v>225230</v>
       </c>
       <c r="E17" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B17,受注ログ!$B$4:$B$205,"&lt;="&amp;C17)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B17,受注ログ!$B$4:$B$5000,"&lt;="&amp;C17)</f>
         <v>316208</v>
       </c>
       <c r="F17" s="14">
@@ -19213,11 +19204,11 @@
         <v>46250</v>
       </c>
       <c r="D18" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B18,受注ログ!$B$4:$B$205,"&lt;="&amp;C18)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B18,受注ログ!$B$4:$B$5000,"&lt;="&amp;C18)</f>
         <v>273320</v>
       </c>
       <c r="E18" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B18,受注ログ!$B$4:$B$205,"&lt;="&amp;C18)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B18,受注ログ!$B$4:$B$5000,"&lt;="&amp;C18)</f>
         <v>268854</v>
       </c>
       <c r="F18" s="14">
@@ -19258,11 +19249,11 @@
         <v>46257</v>
       </c>
       <c r="D19" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B19,受注ログ!$B$4:$B$205,"&lt;="&amp;C19)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B19,受注ログ!$B$4:$B$5000,"&lt;="&amp;C19)</f>
         <v>180639</v>
       </c>
       <c r="E19" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B19,受注ログ!$B$4:$B$205,"&lt;="&amp;C19)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B19,受注ログ!$B$4:$B$5000,"&lt;="&amp;C19)</f>
         <v>206145</v>
       </c>
       <c r="F19" s="14">
@@ -19303,11 +19294,11 @@
         <v>46264</v>
       </c>
       <c r="D20" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B20,受注ログ!$B$4:$B$205,"&lt;="&amp;C20)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B20,受注ログ!$B$4:$B$5000,"&lt;="&amp;C20)</f>
         <v>247566</v>
       </c>
       <c r="E20" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B20,受注ログ!$B$4:$B$205,"&lt;="&amp;C20)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B20,受注ログ!$B$4:$B$5000,"&lt;="&amp;C20)</f>
         <v>65130</v>
       </c>
       <c r="F20" s="14">
@@ -19348,11 +19339,11 @@
         <v>46271</v>
       </c>
       <c r="D21" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B21,受注ログ!$B$4:$B$205,"&lt;="&amp;C21)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B21,受注ログ!$B$4:$B$5000,"&lt;="&amp;C21)</f>
         <v>187564</v>
       </c>
       <c r="E21" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B21,受注ログ!$B$4:$B$205,"&lt;="&amp;C21)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B21,受注ログ!$B$4:$B$5000,"&lt;="&amp;C21)</f>
         <v>167415</v>
       </c>
       <c r="F21" s="14">
@@ -19393,11 +19384,11 @@
         <v>46278</v>
       </c>
       <c r="D22" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B22,受注ログ!$B$4:$B$205,"&lt;="&amp;C22)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B22,受注ログ!$B$4:$B$5000,"&lt;="&amp;C22)</f>
         <v>484729</v>
       </c>
       <c r="E22" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B22,受注ログ!$B$4:$B$205,"&lt;="&amp;C22)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B22,受注ログ!$B$4:$B$5000,"&lt;="&amp;C22)</f>
         <v>120860</v>
       </c>
       <c r="F22" s="14">
@@ -19438,11 +19429,11 @@
         <v>46285</v>
       </c>
       <c r="D23" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B23,受注ログ!$B$4:$B$205,"&lt;="&amp;C23)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B23,受注ログ!$B$4:$B$5000,"&lt;="&amp;C23)</f>
         <v>177253</v>
       </c>
       <c r="E23" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B23,受注ログ!$B$4:$B$205,"&lt;="&amp;C23)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B23,受注ログ!$B$4:$B$5000,"&lt;="&amp;C23)</f>
         <v>263644</v>
       </c>
       <c r="F23" s="14">
@@ -19483,16 +19474,16 @@
         <v>46292</v>
       </c>
       <c r="D24" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B24,受注ログ!$B$4:$B$205,"&lt;="&amp;C24)</f>
-        <v>0</v>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B24,受注ログ!$B$4:$B$5000,"&lt;="&amp;C24)</f>
+        <v>387801</v>
       </c>
       <c r="E24" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B24,受注ログ!$B$4:$B$205,"&lt;="&amp;C24)</f>
-        <v>0</v>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B24,受注ログ!$B$4:$B$5000,"&lt;="&amp;C24)</f>
+        <v>22829</v>
       </c>
       <c r="F24" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>410630</v>
       </c>
       <c r="G24" s="14">
         <f>サマリー!$B$15</f>
@@ -19500,19 +19491,19 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="2"/>
-        <v>-500000</v>
+        <v>-89370</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.82125999999999999</v>
       </c>
       <c r="J24" s="15">
         <f>IFERROR(D24/サマリー!$B$7,0)</f>
-        <v>0</v>
+        <v>1.551204</v>
       </c>
       <c r="K24" s="15">
         <f>IFERROR(E24/サマリー!$B$7,0)</f>
-        <v>0</v>
+        <v>9.1315999999999994E-2</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -19528,11 +19519,11 @@
         <v>46299</v>
       </c>
       <c r="D25" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B25,受注ログ!$B$4:$B$205,"&lt;="&amp;C25)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B25,受注ログ!$B$4:$B$5000,"&lt;="&amp;C25)</f>
         <v>0</v>
       </c>
       <c r="E25" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B25,受注ログ!$B$4:$B$205,"&lt;="&amp;C25)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B25,受注ログ!$B$4:$B$5000,"&lt;="&amp;C25)</f>
         <v>0</v>
       </c>
       <c r="F25" s="14">
@@ -19573,11 +19564,11 @@
         <v>46306</v>
       </c>
       <c r="D26" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B26,受注ログ!$B$4:$B$205,"&lt;="&amp;C26)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B26,受注ログ!$B$4:$B$5000,"&lt;="&amp;C26)</f>
         <v>0</v>
       </c>
       <c r="E26" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B26,受注ログ!$B$4:$B$205,"&lt;="&amp;C26)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B26,受注ログ!$B$4:$B$5000,"&lt;="&amp;C26)</f>
         <v>0</v>
       </c>
       <c r="F26" s="14">
@@ -19618,11 +19609,11 @@
         <v>46313</v>
       </c>
       <c r="D27" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B27,受注ログ!$B$4:$B$205,"&lt;="&amp;C27)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B27,受注ログ!$B$4:$B$5000,"&lt;="&amp;C27)</f>
         <v>0</v>
       </c>
       <c r="E27" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B27,受注ログ!$B$4:$B$205,"&lt;="&amp;C27)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B27,受注ログ!$B$4:$B$5000,"&lt;="&amp;C27)</f>
         <v>0</v>
       </c>
       <c r="F27" s="14">
@@ -19663,11 +19654,11 @@
         <v>46320</v>
       </c>
       <c r="D28" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B28,受注ログ!$B$4:$B$205,"&lt;="&amp;C28)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B28,受注ログ!$B$4:$B$5000,"&lt;="&amp;C28)</f>
         <v>0</v>
       </c>
       <c r="E28" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B28,受注ログ!$B$4:$B$205,"&lt;="&amp;C28)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B28,受注ログ!$B$4:$B$5000,"&lt;="&amp;C28)</f>
         <v>0</v>
       </c>
       <c r="F28" s="14">
@@ -19708,11 +19699,11 @@
         <v>46327</v>
       </c>
       <c r="D29" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B29,受注ログ!$B$4:$B$205,"&lt;="&amp;C29)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B29,受注ログ!$B$4:$B$5000,"&lt;="&amp;C29)</f>
         <v>0</v>
       </c>
       <c r="E29" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B29,受注ログ!$B$4:$B$205,"&lt;="&amp;C29)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B29,受注ログ!$B$4:$B$5000,"&lt;="&amp;C29)</f>
         <v>0</v>
       </c>
       <c r="F29" s="14">
@@ -19753,11 +19744,11 @@
         <v>46334</v>
       </c>
       <c r="D30" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B30,受注ログ!$B$4:$B$205,"&lt;="&amp;C30)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B30,受注ログ!$B$4:$B$5000,"&lt;="&amp;C30)</f>
         <v>0</v>
       </c>
       <c r="E30" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B30,受注ログ!$B$4:$B$205,"&lt;="&amp;C30)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B30,受注ログ!$B$4:$B$5000,"&lt;="&amp;C30)</f>
         <v>0</v>
       </c>
       <c r="F30" s="14">
@@ -19798,11 +19789,11 @@
         <v>46341</v>
       </c>
       <c r="D31" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B31,受注ログ!$B$4:$B$205,"&lt;="&amp;C31)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B31,受注ログ!$B$4:$B$5000,"&lt;="&amp;C31)</f>
         <v>0</v>
       </c>
       <c r="E31" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B31,受注ログ!$B$4:$B$205,"&lt;="&amp;C31)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B31,受注ログ!$B$4:$B$5000,"&lt;="&amp;C31)</f>
         <v>0</v>
       </c>
       <c r="F31" s="14">
@@ -19843,11 +19834,11 @@
         <v>46348</v>
       </c>
       <c r="D32" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B32,受注ログ!$B$4:$B$205,"&lt;="&amp;C32)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B32,受注ログ!$B$4:$B$5000,"&lt;="&amp;C32)</f>
         <v>0</v>
       </c>
       <c r="E32" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B32,受注ログ!$B$4:$B$205,"&lt;="&amp;C32)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B32,受注ログ!$B$4:$B$5000,"&lt;="&amp;C32)</f>
         <v>0</v>
       </c>
       <c r="F32" s="14">
@@ -19888,11 +19879,11 @@
         <v>46355</v>
       </c>
       <c r="D33" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B33,受注ログ!$B$4:$B$205,"&lt;="&amp;C33)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B33,受注ログ!$B$4:$B$5000,"&lt;="&amp;C33)</f>
         <v>0</v>
       </c>
       <c r="E33" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B33,受注ログ!$B$4:$B$205,"&lt;="&amp;C33)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B33,受注ログ!$B$4:$B$5000,"&lt;="&amp;C33)</f>
         <v>0</v>
       </c>
       <c r="F33" s="14">
@@ -19933,11 +19924,11 @@
         <v>46362</v>
       </c>
       <c r="D34" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B34,受注ログ!$B$4:$B$205,"&lt;="&amp;C34)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B34,受注ログ!$B$4:$B$5000,"&lt;="&amp;C34)</f>
         <v>0</v>
       </c>
       <c r="E34" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B34,受注ログ!$B$4:$B$205,"&lt;="&amp;C34)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B34,受注ログ!$B$4:$B$5000,"&lt;="&amp;C34)</f>
         <v>0</v>
       </c>
       <c r="F34" s="14">
@@ -19978,11 +19969,11 @@
         <v>46369</v>
       </c>
       <c r="D35" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B35,受注ログ!$B$4:$B$205,"&lt;="&amp;C35)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B35,受注ログ!$B$4:$B$5000,"&lt;="&amp;C35)</f>
         <v>0</v>
       </c>
       <c r="E35" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B35,受注ログ!$B$4:$B$205,"&lt;="&amp;C35)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B35,受注ログ!$B$4:$B$5000,"&lt;="&amp;C35)</f>
         <v>0</v>
       </c>
       <c r="F35" s="14">
@@ -20023,11 +20014,11 @@
         <v>46376</v>
       </c>
       <c r="D36" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B36,受注ログ!$B$4:$B$205,"&lt;="&amp;C36)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B36,受注ログ!$B$4:$B$5000,"&lt;="&amp;C36)</f>
         <v>0</v>
       </c>
       <c r="E36" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B36,受注ログ!$B$4:$B$205,"&lt;="&amp;C36)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B36,受注ログ!$B$4:$B$5000,"&lt;="&amp;C36)</f>
         <v>0</v>
       </c>
       <c r="F36" s="14">
@@ -20068,11 +20059,11 @@
         <v>46383</v>
       </c>
       <c r="D37" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B37,受注ログ!$B$4:$B$205,"&lt;="&amp;C37)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B37,受注ログ!$B$4:$B$5000,"&lt;="&amp;C37)</f>
         <v>0</v>
       </c>
       <c r="E37" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B37,受注ログ!$B$4:$B$205,"&lt;="&amp;C37)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B37,受注ログ!$B$4:$B$5000,"&lt;="&amp;C37)</f>
         <v>0</v>
       </c>
       <c r="F37" s="14">
@@ -20113,11 +20104,11 @@
         <v>46390</v>
       </c>
       <c r="D38" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B38,受注ログ!$B$4:$B$205,"&lt;="&amp;C38)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B38,受注ログ!$B$4:$B$5000,"&lt;="&amp;C38)</f>
         <v>0</v>
       </c>
       <c r="E38" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B38,受注ログ!$B$4:$B$205,"&lt;="&amp;C38)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B38,受注ログ!$B$4:$B$5000,"&lt;="&amp;C38)</f>
         <v>0</v>
       </c>
       <c r="F38" s="14">
@@ -20158,11 +20149,11 @@
         <v>46397</v>
       </c>
       <c r="D39" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B39,受注ログ!$B$4:$B$205,"&lt;="&amp;C39)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B39,受注ログ!$B$4:$B$5000,"&lt;="&amp;C39)</f>
         <v>0</v>
       </c>
       <c r="E39" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B39,受注ログ!$B$4:$B$205,"&lt;="&amp;C39)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B39,受注ログ!$B$4:$B$5000,"&lt;="&amp;C39)</f>
         <v>0</v>
       </c>
       <c r="F39" s="14">
@@ -20203,11 +20194,11 @@
         <v>46404</v>
       </c>
       <c r="D40" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B40,受注ログ!$B$4:$B$205,"&lt;="&amp;C40)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B40,受注ログ!$B$4:$B$5000,"&lt;="&amp;C40)</f>
         <v>0</v>
       </c>
       <c r="E40" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B40,受注ログ!$B$4:$B$205,"&lt;="&amp;C40)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B40,受注ログ!$B$4:$B$5000,"&lt;="&amp;C40)</f>
         <v>0</v>
       </c>
       <c r="F40" s="14">
@@ -20248,11 +20239,11 @@
         <v>46411</v>
       </c>
       <c r="D41" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B41,受注ログ!$B$4:$B$205,"&lt;="&amp;C41)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B41,受注ログ!$B$4:$B$5000,"&lt;="&amp;C41)</f>
         <v>0</v>
       </c>
       <c r="E41" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B41,受注ログ!$B$4:$B$205,"&lt;="&amp;C41)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B41,受注ログ!$B$4:$B$5000,"&lt;="&amp;C41)</f>
         <v>0</v>
       </c>
       <c r="F41" s="14">
@@ -20293,11 +20284,11 @@
         <v>46418</v>
       </c>
       <c r="D42" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B42,受注ログ!$B$4:$B$205,"&lt;="&amp;C42)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B42,受注ログ!$B$4:$B$5000,"&lt;="&amp;C42)</f>
         <v>0</v>
       </c>
       <c r="E42" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B42,受注ログ!$B$4:$B$205,"&lt;="&amp;C42)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B42,受注ログ!$B$4:$B$5000,"&lt;="&amp;C42)</f>
         <v>0</v>
       </c>
       <c r="F42" s="14">
@@ -20338,11 +20329,11 @@
         <v>46425</v>
       </c>
       <c r="D43" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B43,受注ログ!$B$4:$B$205,"&lt;="&amp;C43)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B43,受注ログ!$B$4:$B$5000,"&lt;="&amp;C43)</f>
         <v>0</v>
       </c>
       <c r="E43" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B43,受注ログ!$B$4:$B$205,"&lt;="&amp;C43)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B43,受注ログ!$B$4:$B$5000,"&lt;="&amp;C43)</f>
         <v>0</v>
       </c>
       <c r="F43" s="14">
@@ -20383,11 +20374,11 @@
         <v>46432</v>
       </c>
       <c r="D44" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B44,受注ログ!$B$4:$B$205,"&lt;="&amp;C44)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B44,受注ログ!$B$4:$B$5000,"&lt;="&amp;C44)</f>
         <v>0</v>
       </c>
       <c r="E44" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B44,受注ログ!$B$4:$B$205,"&lt;="&amp;C44)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B44,受注ログ!$B$4:$B$5000,"&lt;="&amp;C44)</f>
         <v>0</v>
       </c>
       <c r="F44" s="14">
@@ -20428,11 +20419,11 @@
         <v>46439</v>
       </c>
       <c r="D45" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B45,受注ログ!$B$4:$B$205,"&lt;="&amp;C45)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B45,受注ログ!$B$4:$B$5000,"&lt;="&amp;C45)</f>
         <v>0</v>
       </c>
       <c r="E45" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B45,受注ログ!$B$4:$B$205,"&lt;="&amp;C45)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B45,受注ログ!$B$4:$B$5000,"&lt;="&amp;C45)</f>
         <v>0</v>
       </c>
       <c r="F45" s="14">
@@ -20473,11 +20464,11 @@
         <v>46446</v>
       </c>
       <c r="D46" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B46,受注ログ!$B$4:$B$205,"&lt;="&amp;C46)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B46,受注ログ!$B$4:$B$5000,"&lt;="&amp;C46)</f>
         <v>0</v>
       </c>
       <c r="E46" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B46,受注ログ!$B$4:$B$205,"&lt;="&amp;C46)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B46,受注ログ!$B$4:$B$5000,"&lt;="&amp;C46)</f>
         <v>0</v>
       </c>
       <c r="F46" s="14">
@@ -20518,11 +20509,11 @@
         <v>46453</v>
       </c>
       <c r="D47" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B47,受注ログ!$B$4:$B$205,"&lt;="&amp;C47)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B47,受注ログ!$B$4:$B$5000,"&lt;="&amp;C47)</f>
         <v>0</v>
       </c>
       <c r="E47" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B47,受注ログ!$B$4:$B$205,"&lt;="&amp;C47)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B47,受注ログ!$B$4:$B$5000,"&lt;="&amp;C47)</f>
         <v>0</v>
       </c>
       <c r="F47" s="14">
@@ -20563,11 +20554,11 @@
         <v>46460</v>
       </c>
       <c r="D48" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B48,受注ログ!$B$4:$B$205,"&lt;="&amp;C48)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B48,受注ログ!$B$4:$B$5000,"&lt;="&amp;C48)</f>
         <v>0</v>
       </c>
       <c r="E48" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B48,受注ログ!$B$4:$B$205,"&lt;="&amp;C48)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B48,受注ログ!$B$4:$B$5000,"&lt;="&amp;C48)</f>
         <v>0</v>
       </c>
       <c r="F48" s="14">
@@ -20608,11 +20599,11 @@
         <v>46467</v>
       </c>
       <c r="D49" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B49,受注ログ!$B$4:$B$205,"&lt;="&amp;C49)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B49,受注ログ!$B$4:$B$5000,"&lt;="&amp;C49)</f>
         <v>0</v>
       </c>
       <c r="E49" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B49,受注ログ!$B$4:$B$205,"&lt;="&amp;C49)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B49,受注ログ!$B$4:$B$5000,"&lt;="&amp;C49)</f>
         <v>0</v>
       </c>
       <c r="F49" s="14">
@@ -20653,11 +20644,11 @@
         <v>46474</v>
       </c>
       <c r="D50" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B50,受注ログ!$B$4:$B$205,"&lt;="&amp;C50)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B50,受注ログ!$B$4:$B$5000,"&lt;="&amp;C50)</f>
         <v>0</v>
       </c>
       <c r="E50" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B50,受注ログ!$B$4:$B$205,"&lt;="&amp;C50)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B50,受注ログ!$B$4:$B$5000,"&lt;="&amp;C50)</f>
         <v>0</v>
       </c>
       <c r="F50" s="14">
@@ -20698,11 +20689,11 @@
         <v>46481</v>
       </c>
       <c r="D51" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B51,受注ログ!$B$4:$B$205,"&lt;="&amp;C51)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B51,受注ログ!$B$4:$B$5000,"&lt;="&amp;C51)</f>
         <v>0</v>
       </c>
       <c r="E51" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B51,受注ログ!$B$4:$B$205,"&lt;="&amp;C51)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B51,受注ログ!$B$4:$B$5000,"&lt;="&amp;C51)</f>
         <v>0</v>
       </c>
       <c r="F51" s="14">
@@ -20743,11 +20734,11 @@
         <v>46488</v>
       </c>
       <c r="D52" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B52,受注ログ!$B$4:$B$205,"&lt;="&amp;C52)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B52,受注ログ!$B$4:$B$5000,"&lt;="&amp;C52)</f>
         <v>0</v>
       </c>
       <c r="E52" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B52,受注ログ!$B$4:$B$205,"&lt;="&amp;C52)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B52,受注ログ!$B$4:$B$5000,"&lt;="&amp;C52)</f>
         <v>0</v>
       </c>
       <c r="F52" s="14">
@@ -20788,11 +20779,11 @@
         <v>46495</v>
       </c>
       <c r="D53" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B53,受注ログ!$B$4:$B$205,"&lt;="&amp;C53)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B53,受注ログ!$B$4:$B$5000,"&lt;="&amp;C53)</f>
         <v>0</v>
       </c>
       <c r="E53" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B53,受注ログ!$B$4:$B$205,"&lt;="&amp;C53)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B53,受注ログ!$B$4:$B$5000,"&lt;="&amp;C53)</f>
         <v>0</v>
       </c>
       <c r="F53" s="14">
@@ -20833,11 +20824,11 @@
         <v>46502</v>
       </c>
       <c r="D54" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B54,受注ログ!$B$4:$B$205,"&lt;="&amp;C54)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B54,受注ログ!$B$4:$B$5000,"&lt;="&amp;C54)</f>
         <v>0</v>
       </c>
       <c r="E54" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B54,受注ログ!$B$4:$B$205,"&lt;="&amp;C54)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B54,受注ログ!$B$4:$B$5000,"&lt;="&amp;C54)</f>
         <v>0</v>
       </c>
       <c r="F54" s="14">
@@ -20878,11 +20869,11 @@
         <v>46509</v>
       </c>
       <c r="D55" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B55,受注ログ!$B$4:$B$205,"&lt;="&amp;C55)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B55,受注ログ!$B$4:$B$5000,"&lt;="&amp;C55)</f>
         <v>0</v>
       </c>
       <c r="E55" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B55,受注ログ!$B$4:$B$205,"&lt;="&amp;C55)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B55,受注ログ!$B$4:$B$5000,"&lt;="&amp;C55)</f>
         <v>0</v>
       </c>
       <c r="F55" s="14">
@@ -20923,11 +20914,11 @@
         <v>46516</v>
       </c>
       <c r="D56" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B56,受注ログ!$B$4:$B$205,"&lt;="&amp;C56)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B56,受注ログ!$B$4:$B$5000,"&lt;="&amp;C56)</f>
         <v>0</v>
       </c>
       <c r="E56" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B56,受注ログ!$B$4:$B$205,"&lt;="&amp;C56)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B56,受注ログ!$B$4:$B$5000,"&lt;="&amp;C56)</f>
         <v>0</v>
       </c>
       <c r="F56" s="14">
@@ -20956,19 +20947,19 @@
       </c>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B58" s="41"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="41"/>
-      <c r="K58" s="41"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21055,11 +21046,11 @@
         <v>46173</v>
       </c>
       <c r="D3" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B3,受注ログ!$B$4:$B$205,"&lt;="&amp;C3)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B3,受注ログ!$B$4:$B$5000,"&lt;="&amp;C3)</f>
         <v>0</v>
       </c>
       <c r="E3" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B3,受注ログ!$B$4:$B$205,"&lt;="&amp;C3)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B3,受注ログ!$B$4:$B$5000,"&lt;="&amp;C3)</f>
         <v>0</v>
       </c>
       <c r="F3" s="14">
@@ -21100,11 +21091,11 @@
         <v>46203</v>
       </c>
       <c r="D4" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B4,受注ログ!$B$4:$B$205,"&lt;="&amp;C4)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B4,受注ログ!$B$4:$B$5000,"&lt;="&amp;C4)</f>
         <v>91004</v>
       </c>
       <c r="E4" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B4,受注ログ!$B$4:$B$205,"&lt;="&amp;C4)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B4,受注ログ!$B$4:$B$5000,"&lt;="&amp;C4)</f>
         <v>27872</v>
       </c>
       <c r="F4" s="14">
@@ -21145,11 +21136,11 @@
         <v>46234</v>
       </c>
       <c r="D5" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B5,受注ログ!$B$4:$B$205,"&lt;="&amp;C5)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B5,受注ログ!$B$4:$B$5000,"&lt;="&amp;C5)</f>
         <v>1056778</v>
       </c>
       <c r="E5" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B5,受注ログ!$B$4:$B$205,"&lt;="&amp;C5)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B5,受注ログ!$B$4:$B$5000,"&lt;="&amp;C5)</f>
         <v>639108</v>
       </c>
       <c r="F5" s="14">
@@ -21190,11 +21181,11 @@
         <v>46265</v>
       </c>
       <c r="D6" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B6,受注ログ!$B$4:$B$205,"&lt;="&amp;C6)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B6,受注ログ!$B$4:$B$5000,"&lt;="&amp;C6)</f>
         <v>1102988</v>
       </c>
       <c r="E6" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B6,受注ログ!$B$4:$B$205,"&lt;="&amp;C6)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B6,受注ログ!$B$4:$B$5000,"&lt;="&amp;C6)</f>
         <v>957083</v>
       </c>
       <c r="F6" s="14">
@@ -21235,16 +21226,16 @@
         <v>46295</v>
       </c>
       <c r="D7" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B7,受注ログ!$B$4:$B$205,"&lt;="&amp;C7)</f>
-        <v>841291</v>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B7,受注ログ!$B$4:$B$5000,"&lt;="&amp;C7)</f>
+        <v>1229092</v>
       </c>
       <c r="E7" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B7,受注ログ!$B$4:$B$205,"&lt;="&amp;C7)</f>
-        <v>519119</v>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B7,受注ログ!$B$4:$B$5000,"&lt;="&amp;C7)</f>
+        <v>541948</v>
       </c>
       <c r="F7" s="14">
         <f t="shared" si="1"/>
-        <v>1360410</v>
+        <v>1771040</v>
       </c>
       <c r="G7" s="14">
         <f>サマリー!$B$16</f>
@@ -21252,19 +21243,19 @@
       </c>
       <c r="H7" s="33">
         <f t="shared" si="2"/>
-        <v>-639590</v>
+        <v>-228960</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="3"/>
-        <v>0.68020499999999995</v>
+        <v>0.88551999999999997</v>
       </c>
       <c r="J7" s="15">
         <f>IFERROR(D7/サマリー!$B$8,0)</f>
-        <v>0.84129100000000001</v>
+        <v>1.2290920000000001</v>
       </c>
       <c r="K7" s="15">
         <f>IFERROR(E7/サマリー!$B$8,0)</f>
-        <v>0.519119</v>
+        <v>0.54194799999999999</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -21280,11 +21271,11 @@
         <v>46326</v>
       </c>
       <c r="D8" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B8,受注ログ!$B$4:$B$205,"&lt;="&amp;C8)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B8,受注ログ!$B$4:$B$5000,"&lt;="&amp;C8)</f>
         <v>0</v>
       </c>
       <c r="E8" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B8,受注ログ!$B$4:$B$205,"&lt;="&amp;C8)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B8,受注ログ!$B$4:$B$5000,"&lt;="&amp;C8)</f>
         <v>0</v>
       </c>
       <c r="F8" s="14">
@@ -21325,11 +21316,11 @@
         <v>46356</v>
       </c>
       <c r="D9" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B9,受注ログ!$B$4:$B$205,"&lt;="&amp;C9)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B9,受注ログ!$B$4:$B$5000,"&lt;="&amp;C9)</f>
         <v>0</v>
       </c>
       <c r="E9" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B9,受注ログ!$B$4:$B$205,"&lt;="&amp;C9)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B9,受注ログ!$B$4:$B$5000,"&lt;="&amp;C9)</f>
         <v>0</v>
       </c>
       <c r="F9" s="14">
@@ -21370,11 +21361,11 @@
         <v>46387</v>
       </c>
       <c r="D10" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B10,受注ログ!$B$4:$B$205,"&lt;="&amp;C10)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B10,受注ログ!$B$4:$B$5000,"&lt;="&amp;C10)</f>
         <v>0</v>
       </c>
       <c r="E10" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B10,受注ログ!$B$4:$B$205,"&lt;="&amp;C10)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B10,受注ログ!$B$4:$B$5000,"&lt;="&amp;C10)</f>
         <v>0</v>
       </c>
       <c r="F10" s="14">
@@ -21415,11 +21406,11 @@
         <v>46418</v>
       </c>
       <c r="D11" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B11,受注ログ!$B$4:$B$205,"&lt;="&amp;C11)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B11,受注ログ!$B$4:$B$5000,"&lt;="&amp;C11)</f>
         <v>0</v>
       </c>
       <c r="E11" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B11,受注ログ!$B$4:$B$205,"&lt;="&amp;C11)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B11,受注ログ!$B$4:$B$5000,"&lt;="&amp;C11)</f>
         <v>0</v>
       </c>
       <c r="F11" s="14">
@@ -21460,11 +21451,11 @@
         <v>46446</v>
       </c>
       <c r="D12" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B12,受注ログ!$B$4:$B$205,"&lt;="&amp;C12)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B12,受注ログ!$B$4:$B$5000,"&lt;="&amp;C12)</f>
         <v>0</v>
       </c>
       <c r="E12" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B12,受注ログ!$B$4:$B$205,"&lt;="&amp;C12)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B12,受注ログ!$B$4:$B$5000,"&lt;="&amp;C12)</f>
         <v>0</v>
       </c>
       <c r="F12" s="14">
@@ -21505,11 +21496,11 @@
         <v>46477</v>
       </c>
       <c r="D13" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B13,受注ログ!$B$4:$B$205,"&lt;="&amp;C13)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B13,受注ログ!$B$4:$B$5000,"&lt;="&amp;C13)</f>
         <v>0</v>
       </c>
       <c r="E13" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B13,受注ログ!$B$4:$B$205,"&lt;="&amp;C13)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B13,受注ログ!$B$4:$B$5000,"&lt;="&amp;C13)</f>
         <v>0</v>
       </c>
       <c r="F13" s="14">
@@ -21550,11 +21541,11 @@
         <v>46507</v>
       </c>
       <c r="D14" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B14,受注ログ!$B$4:$B$205,"&lt;="&amp;C14)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B14,受注ログ!$B$4:$B$5000,"&lt;="&amp;C14)</f>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B14,受注ログ!$B$4:$B$205,"&lt;="&amp;C14)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B14,受注ログ!$B$4:$B$5000,"&lt;="&amp;C14)</f>
         <v>0</v>
       </c>
       <c r="F14" s="14">
@@ -21595,11 +21586,11 @@
         <v>46538</v>
       </c>
       <c r="D15" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B15,受注ログ!$B$4:$B$205,"&lt;="&amp;C15)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B15,受注ログ!$B$4:$B$5000,"&lt;="&amp;C15)</f>
         <v>0</v>
       </c>
       <c r="E15" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B15,受注ログ!$B$4:$B$205,"&lt;="&amp;C15)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B15,受注ログ!$B$4:$B$5000,"&lt;="&amp;C15)</f>
         <v>0</v>
       </c>
       <c r="F15" s="14">
@@ -21703,16 +21694,16 @@
         <v>46326</v>
       </c>
       <c r="D3" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B3,受注ログ!$B$4:$B$205,"&lt;="&amp;C3)</f>
-        <v>3092061</v>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B3,受注ログ!$B$4:$B$5000,"&lt;="&amp;C3)</f>
+        <v>3479862</v>
       </c>
       <c r="E3" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B3,受注ログ!$B$4:$B$205,"&lt;="&amp;C3)</f>
-        <v>2143182</v>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B3,受注ログ!$B$4:$B$5000,"&lt;="&amp;C3)</f>
+        <v>2166011</v>
       </c>
       <c r="F3" s="14">
         <f>D3+E3</f>
-        <v>5235243</v>
+        <v>5645873</v>
       </c>
       <c r="G3" s="14">
         <f>サマリー!$B$17</f>
@@ -21720,11 +21711,11 @@
       </c>
       <c r="H3" s="33">
         <f>F3-G3</f>
-        <v>-6764757</v>
+        <v>-6354127</v>
       </c>
       <c r="I3" s="15">
         <f>IFERROR(F3/G3,0)</f>
-        <v>0.43627025000000003</v>
+        <v>0.47048941666666666</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -21740,11 +21731,11 @@
         <v>46507</v>
       </c>
       <c r="D4" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B4,受注ログ!$B$4:$B$205,"&lt;="&amp;C4)</f>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B4,受注ログ!$B$4:$B$5000,"&lt;="&amp;C4)</f>
         <v>0</v>
       </c>
       <c r="E4" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B4,受注ログ!$B$4:$B$205,"&lt;="&amp;C4)</f>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B4,受注ログ!$B$4:$B$5000,"&lt;="&amp;C4)</f>
         <v>0</v>
       </c>
       <c r="F4" s="14">
@@ -21777,16 +21768,16 @@
         <v>46507</v>
       </c>
       <c r="D5" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B5,受注ログ!$B$4:$B$205,"&lt;="&amp;C5)</f>
-        <v>3092061</v>
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B5,受注ログ!$B$4:$B$5000,"&lt;="&amp;C5)</f>
+        <v>3479862</v>
       </c>
       <c r="E5" s="14">
-        <f>SUMIFS(受注ログ!$D$4:$D$205,受注ログ!$B$4:$B$205,"&gt;="&amp;B5,受注ログ!$B$4:$B$205,"&lt;="&amp;C5)</f>
-        <v>2143182</v>
+        <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B5,受注ログ!$B$4:$B$5000,"&lt;="&amp;C5)</f>
+        <v>2166011</v>
       </c>
       <c r="F5" s="14">
         <f>D5+E5</f>
-        <v>5235243</v>
+        <v>5645873</v>
       </c>
       <c r="G5" s="14">
         <f>サマリー!$B$18</f>
@@ -21794,11 +21785,11 @@
       </c>
       <c r="H5" s="33">
         <f>F5-G5</f>
-        <v>-18764757</v>
+        <v>-18354127</v>
       </c>
       <c r="I5" s="15">
         <f>IFERROR(F5/G5,0)</f>
-        <v>0.21813512500000001</v>
+        <v>0.23524470833333333</v>
       </c>
     </row>
   </sheetData>
@@ -21909,18 +21900,18 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/売上管理_受注ログ版 (6).xlsx
+++ b/売上管理_受注ログ版 (6).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\重要AI用\売上ルーム\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\uriage-kanri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786EF222-800B-451F-A9C9-D35E1818E354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1081F4F1-D286-4EC5-B0E2-AD38D21EF8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="1620" windowWidth="25245" windowHeight="13755" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/売上管理_受注ログ版 (6).xlsx
+++ b/売上管理_受注ログ版 (6).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\uriage-kanri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1081F4F1-D286-4EC5-B0E2-AD38D21EF8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B53DD7F-DA59-4576-858F-F248766D95B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="1620" windowWidth="25245" windowHeight="13755" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2778,17 +2778,17 @@
         <f>B7</f>
         <v>250000</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="14" t="e">
         <f ca="1">INDEX(週次集計!D3:D56,$B$20)</f>
-        <v>387801</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D26" s="15">
         <f ca="1">IFERROR(C26/B26,0)</f>
-        <v>1.551204</v>
-      </c>
-      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="E26" s="14" t="e">
         <f ca="1">MAX(B26-C26,0)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2893,13 +2893,13 @@
         <f>B7</f>
         <v>250000</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="14" t="e">
         <f ca="1">INDEX(週次集計!D3:D56,$B$20)</f>
-        <v>387801</v>
-      </c>
-      <c r="D34" s="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D34" s="14" t="e">
         <f t="shared" ref="D34:D41" ca="1" si="0">MAX(B34-C34,0)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E34" s="17">
         <f ca="1">INDEX(週次集計!C3:C56,$B$20)</f>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="H34" s="19">
         <f t="shared" ref="H34:H41" ca="1" si="3">RANK(G34,$G$34:$G$41)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2959,13 +2959,13 @@
         <f>B15</f>
         <v>500000</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="14" t="e">
         <f ca="1">INDEX(週次集計!F3:F56,$B$20)</f>
-        <v>410630</v>
-      </c>
-      <c r="D36" s="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D36" s="14" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>89370</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E36" s="17">
         <f ca="1">INDEX(週次集計!C3:C56,$B$20)</f>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G36" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>22342.5</v>
+        <v>0</v>
       </c>
       <c r="H36" s="19">
         <f t="shared" ca="1" si="3"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="H37" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3561,21 +3561,21 @@
     </row>
     <row r="3" spans="1:53" ht="19.5" customHeight="1">
       <c r="A3" s="23"/>
-      <c r="B3" s="23">
+      <c r="B3" s="23" t="e">
         <f ca="1">MAX(サマリー!$B$7-INDEX(週次集計!$D$3:$D$56,サマリー!$B$20),0)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="C3" s="23">
         <f ca="1">MAX(サマリー!$B$7-INDEX(週次集計!$E$3:$E$56,サマリー!$B$20),0)</f>
         <v>227171</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="23" t="e">
         <f ca="1">INDEX(週次集計!$F$3:$F$56,サマリー!$B$20)</f>
-        <v>410630</v>
-      </c>
-      <c r="E3" s="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E3" s="23" t="e">
         <f ca="1">MAX(サマリー!$B$15-INDEX(週次集計!$F$3:$F$56,サマリー!$B$20),0)</f>
-        <v>89370</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F3" s="23">
         <f ca="1">SUMIFS($C$6:$C$205,$B$6:$B$205,TODAY())</f>
@@ -19473,33 +19473,33 @@
         <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="D24" s="14">
-        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B24,受注ログ!$B$4:$B$5000,"&lt;="&amp;C24)</f>
-        <v>387801</v>
+      <c r="D24" s="14" t="e">
+        <f>SUMIFS(受注ログ!$C$4:$C$50000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B24,受注ログ!$B$4:$B$5000,"&lt;="&amp;C24)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E24" s="14">
         <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B24,受注ログ!$B$4:$B$5000,"&lt;="&amp;C24)</f>
         <v>22829</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="14" t="e">
         <f t="shared" si="1"/>
-        <v>410630</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G24" s="14">
         <f>サマリー!$B$15</f>
         <v>500000</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="33" t="e">
         <f t="shared" si="2"/>
-        <v>-89370</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="3"/>
-        <v>0.82125999999999999</v>
+        <v>0</v>
       </c>
       <c r="J24" s="15">
         <f>IFERROR(D24/サマリー!$B$7,0)</f>
-        <v>1.551204</v>
+        <v>0</v>
       </c>
       <c r="K24" s="15">
         <f>IFERROR(E24/サマリー!$B$7,0)</f>

--- a/売上管理_受注ログ版 (6).xlsx
+++ b/売上管理_受注ログ版 (6).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\uriage-kanri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B53DD7F-DA59-4576-858F-F248766D95B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD76F3AA-9442-45F9-9AFB-71A8DA38414F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="1620" windowWidth="25245" windowHeight="13755" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2778,17 +2778,17 @@
         <f>B7</f>
         <v>250000</v>
       </c>
-      <c r="C26" s="14" t="e">
+      <c r="C26" s="14">
         <f ca="1">INDEX(週次集計!D3:D56,$B$20)</f>
-        <v>#VALUE!</v>
+        <v>387801</v>
       </c>
       <c r="D26" s="15">
         <f ca="1">IFERROR(C26/B26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="14" t="e">
+        <v>1.551204</v>
+      </c>
+      <c r="E26" s="14">
         <f ca="1">MAX(B26-C26,0)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2893,13 +2893,13 @@
         <f>B7</f>
         <v>250000</v>
       </c>
-      <c r="C34" s="14" t="e">
+      <c r="C34" s="14">
         <f ca="1">INDEX(週次集計!D3:D56,$B$20)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D34" s="14" t="e">
+        <v>387801</v>
+      </c>
+      <c r="D34" s="14">
         <f t="shared" ref="D34:D41" ca="1" si="0">MAX(B34-C34,0)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="E34" s="17">
         <f ca="1">INDEX(週次集計!C3:C56,$B$20)</f>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="H34" s="19">
         <f t="shared" ref="H34:H41" ca="1" si="3">RANK(G34,$G$34:$G$41)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2959,13 +2959,13 @@
         <f>B15</f>
         <v>500000</v>
       </c>
-      <c r="C36" s="14" t="e">
+      <c r="C36" s="14">
         <f ca="1">INDEX(週次集計!F3:F56,$B$20)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D36" s="14" t="e">
+        <v>410630</v>
+      </c>
+      <c r="D36" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>89370</v>
       </c>
       <c r="E36" s="17">
         <f ca="1">INDEX(週次集計!C3:C56,$B$20)</f>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G36" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>22342.5</v>
       </c>
       <c r="H36" s="19">
         <f t="shared" ca="1" si="3"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="H37" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3561,21 +3561,21 @@
     </row>
     <row r="3" spans="1:53" ht="19.5" customHeight="1">
       <c r="A3" s="23"/>
-      <c r="B3" s="23" t="e">
+      <c r="B3" s="23">
         <f ca="1">MAX(サマリー!$B$7-INDEX(週次集計!$D$3:$D$56,サマリー!$B$20),0)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="C3" s="23">
         <f ca="1">MAX(サマリー!$B$7-INDEX(週次集計!$E$3:$E$56,サマリー!$B$20),0)</f>
         <v>227171</v>
       </c>
-      <c r="D3" s="23" t="e">
+      <c r="D3" s="23">
         <f ca="1">INDEX(週次集計!$F$3:$F$56,サマリー!$B$20)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E3" s="23" t="e">
+        <v>410630</v>
+      </c>
+      <c r="E3" s="23">
         <f ca="1">MAX(サマリー!$B$15-INDEX(週次集計!$F$3:$F$56,サマリー!$B$20),0)</f>
-        <v>#VALUE!</v>
+        <v>89370</v>
       </c>
       <c r="F3" s="23">
         <f ca="1">SUMIFS($C$6:$C$205,$B$6:$B$205,TODAY())</f>
@@ -19473,33 +19473,33 @@
         <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="D24" s="14" t="e">
-        <f>SUMIFS(受注ログ!$C$4:$C$50000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B24,受注ログ!$B$4:$B$5000,"&lt;="&amp;C24)</f>
-        <v>#VALUE!</v>
+      <c r="D24" s="14">
+        <f>SUMIFS(受注ログ!$C$4:$C$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B24,受注ログ!$B$4:$B$5000,"&lt;="&amp;C24)</f>
+        <v>387801</v>
       </c>
       <c r="E24" s="14">
         <f>SUMIFS(受注ログ!$D$4:$D$5000,受注ログ!$B$4:$B$5000,"&gt;="&amp;B24,受注ログ!$B$4:$B$5000,"&lt;="&amp;C24)</f>
         <v>22829</v>
       </c>
-      <c r="F24" s="14" t="e">
+      <c r="F24" s="14">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>410630</v>
       </c>
       <c r="G24" s="14">
         <f>サマリー!$B$15</f>
         <v>500000</v>
       </c>
-      <c r="H24" s="33" t="e">
+      <c r="H24" s="33">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>-89370</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.82125999999999999</v>
       </c>
       <c r="J24" s="15">
         <f>IFERROR(D24/サマリー!$B$7,0)</f>
-        <v>0</v>
+        <v>1.551204</v>
       </c>
       <c r="K24" s="15">
         <f>IFERROR(E24/サマリー!$B$7,0)</f>
